--- a/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/個別情報画面/個別収支情報画面_表示.xlsx
+++ b/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/個別情報画面/個別収支情報画面_表示.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjk037_\Desktop\学習用\家計管理アプリ\b_詳細設計\画面設計\個別情報画面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B649EAA-6FF8-4CE8-907D-C28FEF8633F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D911981-90B1-4036-BFC2-3C43091746FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13020" yWindow="225" windowWidth="13860" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12510" yWindow="105" windowWidth="13860" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="モード切替で表示が切り替わる対応" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -214,6 +215,129 @@
     <t>戻る</t>
     <rPh sb="0" eb="1">
       <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（消える）</t>
+    <rPh sb="1" eb="2">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編集</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャンセル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンファーム＆フラグを「９」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トグル絵</t>
+    <rPh sb="3" eb="4">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>頑張った</t>
+    <rPh sb="0" eb="2">
+      <t>ガンバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絵</t>
+    <rPh sb="0" eb="1">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長文入力</t>
+    <rPh sb="0" eb="2">
+      <t>チョウブン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数値入力</t>
+    <rPh sb="0" eb="4">
+      <t>スウチニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドロップダウン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収支分類</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カレンダー入力</t>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリーム色</t>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水色</t>
+    <rPh sb="0" eb="2">
+      <t>ミズイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編集モード</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>閲覧モード</t>
+    <rPh sb="0" eb="2">
+      <t>エツラン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -720,4 +844,155 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4CEDEDD-ADB9-4711-8D48-E4D77776A4C2}">
+  <dimension ref="B2:H21"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="2:8">
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>